--- a/base_prov/sams/sams_abbott_2026_10_21.xlsx
+++ b/base_prov/sams/sams_abbott_2026_10_21.xlsx
@@ -605,22 +605,22 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -887,22 +887,22 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -1070,22 +1070,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1733,17 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
